--- a/research/traditional_assets/database/data/indonesia/indonesia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_reinsurance.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.113</v>
-      </c>
-      <c r="E2">
-        <v>-0.119</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
-        <v>0.0746031746031746</v>
+        <v>-0.1778929188255613</v>
       </c>
       <c r="H2">
-        <v>0.0746031746031746</v>
+        <v>-0.1778929188255613</v>
       </c>
       <c r="I2">
-        <v>0.04603174603174603</v>
+        <v>-0.1735751295336788</v>
       </c>
       <c r="J2">
-        <v>0.04603174603174603</v>
+        <v>-0.1735751295336788</v>
       </c>
       <c r="K2">
-        <v>5.19</v>
+        <v>-18.6</v>
       </c>
       <c r="L2">
-        <v>0.04335839598997494</v>
+        <v>-0.1606217616580311</v>
       </c>
       <c r="M2">
-        <v>1.94</v>
+        <v>0.154</v>
       </c>
       <c r="N2">
-        <v>0.0126549249836921</v>
+        <v>0.00107843137254902</v>
       </c>
       <c r="O2">
-        <v>0.373795761078998</v>
+        <v>-0.008279569892473117</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>0.154</v>
       </c>
       <c r="Q2">
-        <v>0.0126549249836921</v>
+        <v>0.00107843137254902</v>
       </c>
       <c r="R2">
-        <v>0.373795761078998</v>
+        <v>-0.008279569892473117</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +633,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.793</v>
+        <v>11</v>
       </c>
       <c r="V2">
-        <v>0.005172863666014351</v>
+        <v>0.07703081232492996</v>
       </c>
       <c r="W2">
-        <v>0.04814471243042672</v>
+        <v>-0.1547420965058236</v>
       </c>
       <c r="X2">
-        <v>0.09987506145934166</v>
+        <v>0.1394330526334751</v>
       </c>
       <c r="Y2">
-        <v>-0.05173034902891494</v>
+        <v>-0.2941751491392988</v>
       </c>
       <c r="Z2">
-        <v>1.12141652613828</v>
+        <v>0.9697923907308617</v>
       </c>
       <c r="AA2">
-        <v>0.05162076072700019</v>
+        <v>-0.1683318398418853</v>
       </c>
       <c r="AB2">
-        <v>0.09987506145934166</v>
+        <v>0.1394330526334751</v>
       </c>
       <c r="AC2">
-        <v>-0.04825430073234147</v>
+        <v>-0.3077648924753604</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.793</v>
+        <v>-11</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.005199761322431102</v>
+        <v>-0.08345978755690439</v>
       </c>
       <c r="AK2">
-        <v>-0.006641151691274381</v>
+        <v>-0.141206675224647</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-0.1328308207705193</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +713,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
-      </c>
-      <c r="E3">
-        <v>-0.119</v>
+        <v>0.12</v>
       </c>
       <c r="G3">
-        <v>0.0746031746031746</v>
+        <v>-0.1778929188255613</v>
       </c>
       <c r="H3">
-        <v>0.0746031746031746</v>
+        <v>-0.1778929188255613</v>
       </c>
       <c r="I3">
-        <v>0.04603174603174603</v>
+        <v>-0.1735751295336788</v>
       </c>
       <c r="J3">
-        <v>0.04603174603174603</v>
+        <v>-0.1735751295336788</v>
       </c>
       <c r="K3">
-        <v>5.19</v>
+        <v>-18.6</v>
       </c>
       <c r="L3">
-        <v>0.04335839598997494</v>
+        <v>-0.1606217616580311</v>
       </c>
       <c r="M3">
-        <v>1.94</v>
+        <v>0.154</v>
       </c>
       <c r="N3">
-        <v>0.0126549249836921</v>
+        <v>0.00107843137254902</v>
       </c>
       <c r="O3">
-        <v>0.373795761078998</v>
+        <v>-0.008279569892473117</v>
       </c>
       <c r="P3">
-        <v>1.94</v>
+        <v>0.154</v>
       </c>
       <c r="Q3">
-        <v>0.0126549249836921</v>
+        <v>0.00107843137254902</v>
       </c>
       <c r="R3">
-        <v>0.373795761078998</v>
+        <v>-0.008279569892473117</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.793</v>
+        <v>11</v>
       </c>
       <c r="V3">
-        <v>0.005172863666014351</v>
+        <v>0.07703081232492996</v>
       </c>
       <c r="W3">
-        <v>0.04814471243042672</v>
+        <v>-0.1547420965058236</v>
       </c>
       <c r="X3">
-        <v>0.09987506145934166</v>
+        <v>0.1394330526334751</v>
       </c>
       <c r="Y3">
-        <v>-0.05173034902891494</v>
+        <v>-0.2941751491392988</v>
       </c>
       <c r="Z3">
-        <v>1.12141652613828</v>
+        <v>0.9697923907308617</v>
       </c>
       <c r="AA3">
-        <v>0.05162076072700019</v>
+        <v>-0.1683318398418853</v>
       </c>
       <c r="AB3">
-        <v>0.09987506145934166</v>
+        <v>0.1394330526334751</v>
       </c>
       <c r="AC3">
-        <v>-0.04825430073234147</v>
+        <v>-0.3077648924753604</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.793</v>
+        <v>-11</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.005199761322431102</v>
+        <v>-0.08345978755690439</v>
       </c>
       <c r="AK3">
-        <v>-0.006641151691274381</v>
+        <v>-0.141206675224647</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-0.1328308207705193</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_reinsurance.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.12</v>
+        <v>0.0851</v>
+      </c>
+      <c r="E2">
+        <v>-0.242</v>
       </c>
       <c r="G2">
-        <v>-0.1778929188255613</v>
+        <v>0.02403035413153457</v>
       </c>
       <c r="H2">
-        <v>-0.1778929188255613</v>
+        <v>0.02403035413153457</v>
       </c>
       <c r="I2">
-        <v>-0.1735751295336788</v>
+        <v>0.0342327150084317</v>
       </c>
       <c r="J2">
-        <v>-0.1735751295336788</v>
+        <v>0.02004832615077135</v>
       </c>
       <c r="K2">
-        <v>-18.6</v>
+        <v>2.53</v>
       </c>
       <c r="L2">
-        <v>-0.1606217616580311</v>
+        <v>0.02133220910623946</v>
       </c>
       <c r="M2">
-        <v>0.154</v>
+        <v>0.45</v>
       </c>
       <c r="N2">
-        <v>0.00107843137254902</v>
+        <v>0.006428571428571428</v>
       </c>
       <c r="O2">
-        <v>-0.008279569892473117</v>
+        <v>0.1778656126482214</v>
       </c>
       <c r="P2">
-        <v>0.154</v>
+        <v>0.45</v>
       </c>
       <c r="Q2">
-        <v>0.00107843137254902</v>
+        <v>0.006428571428571428</v>
       </c>
       <c r="R2">
-        <v>-0.008279569892473117</v>
+        <v>0.1778656126482214</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11</v>
+        <v>0.623</v>
       </c>
       <c r="V2">
-        <v>0.07703081232492996</v>
+        <v>0.0089</v>
       </c>
       <c r="W2">
-        <v>-0.1547420965058236</v>
+        <v>0.02845894263217098</v>
       </c>
       <c r="X2">
-        <v>0.1394330526334751</v>
+        <v>0.1178539234156987</v>
       </c>
       <c r="Y2">
-        <v>-0.2941751491392988</v>
+        <v>-0.08939498078352776</v>
       </c>
       <c r="Z2">
-        <v>0.9697923907308617</v>
+        <v>1.522464698331194</v>
       </c>
       <c r="AA2">
-        <v>-0.1683318398418853</v>
+        <v>0.03052286882517947</v>
       </c>
       <c r="AB2">
-        <v>0.1394330526334751</v>
+        <v>0.1178539234156987</v>
       </c>
       <c r="AC2">
-        <v>-0.3077648924753604</v>
+        <v>-0.08733105459051925</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-11</v>
+        <v>-0.623</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.08345978755690439</v>
+        <v>-0.008979921299566139</v>
       </c>
       <c r="AK2">
-        <v>-0.141206675224647</v>
+        <v>-0.006840365844285604</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5555555555555556</v>
+        <v>-0.1406320541760722</v>
       </c>
     </row>
     <row r="3">
@@ -713,43 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>0.0851</v>
+      </c>
+      <c r="E3">
+        <v>-0.242</v>
       </c>
       <c r="G3">
-        <v>-0.1778929188255613</v>
+        <v>0.02403035413153457</v>
       </c>
       <c r="H3">
-        <v>-0.1778929188255613</v>
+        <v>0.02403035413153457</v>
       </c>
       <c r="I3">
-        <v>-0.1735751295336788</v>
+        <v>0.0342327150084317</v>
       </c>
       <c r="J3">
-        <v>-0.1735751295336788</v>
+        <v>0.02004832615077135</v>
       </c>
       <c r="K3">
-        <v>-18.6</v>
+        <v>2.53</v>
       </c>
       <c r="L3">
-        <v>-0.1606217616580311</v>
+        <v>0.02133220910623946</v>
       </c>
       <c r="M3">
-        <v>0.154</v>
+        <v>0.45</v>
       </c>
       <c r="N3">
-        <v>0.00107843137254902</v>
+        <v>0.006428571428571428</v>
       </c>
       <c r="O3">
-        <v>-0.008279569892473117</v>
+        <v>0.1778656126482214</v>
       </c>
       <c r="P3">
-        <v>0.154</v>
+        <v>0.45</v>
       </c>
       <c r="Q3">
-        <v>0.00107843137254902</v>
+        <v>0.006428571428571428</v>
       </c>
       <c r="R3">
-        <v>-0.008279569892473117</v>
+        <v>0.1778656126482214</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11</v>
+        <v>0.623</v>
       </c>
       <c r="V3">
-        <v>0.07703081232492996</v>
+        <v>0.0089</v>
       </c>
       <c r="W3">
-        <v>-0.1547420965058236</v>
+        <v>0.02845894263217098</v>
       </c>
       <c r="X3">
-        <v>0.1394330526334751</v>
+        <v>0.1178539234156987</v>
       </c>
       <c r="Y3">
-        <v>-0.2941751491392988</v>
+        <v>-0.08939498078352776</v>
       </c>
       <c r="Z3">
-        <v>0.9697923907308617</v>
+        <v>1.522464698331194</v>
       </c>
       <c r="AA3">
-        <v>-0.1683318398418853</v>
+        <v>0.03052286882517947</v>
       </c>
       <c r="AB3">
-        <v>0.1394330526334751</v>
+        <v>0.1178539234156987</v>
       </c>
       <c r="AC3">
-        <v>-0.3077648924753604</v>
+        <v>-0.08733105459051925</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-11</v>
+        <v>-0.623</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08345978755690439</v>
+        <v>-0.008979921299566139</v>
       </c>
       <c r="AK3">
-        <v>-0.141206675224647</v>
+        <v>-0.006840365844285604</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.5555555555555556</v>
+        <v>-0.1406320541760722</v>
       </c>
     </row>
   </sheetData>
